--- a/animaleo_theo_dataset.xlsx
+++ b/animaleo_theo_dataset.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oils" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blend-Oil Pairs" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Assessment" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Single Oils Research" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +63,20 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="002E75B6"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -100,6 +113,16 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -127,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -209,6 +232,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -350,6 +403,21 @@
     <tableColumn id="5" name="# Proconv."/>
     <tableColumn id="6" name="Proconvulsant Oils Present"/>
     <tableColumn id="7" name="Recommendation for Theo"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SinglesTable" displayName="SinglesTable" ref="A7:F76" headerRowCount="1">
+  <autoFilter ref="A7:F76"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Oil"/>
+    <tableColumn id="2" name="Tier"/>
+    <tableColumn id="3" name="In Clean Blend?"/>
+    <tableColumn id="4" name="Evidence / Mechanism"/>
+    <tableColumn id="5" name="Theo-Specific Note"/>
+    <tableColumn id="6" name="Key Source"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -644,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A112"/>
+  <dimension ref="A1:A117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -828,58 +896,58 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>RISK TIER DEFINITIONS</t>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Tab 6 — Single Oils Research: All 69 AnimalEO single oils tiered for active-seizure</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  use (post-ictal + cluster window). Tier A = direct anticonvulsant evidence (10).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CLEAN — No constituents with documented seizure-threshold concern in independent</t>
+          <t xml:space="preserve">  Tier B = calming/anxiolytic for trigger window (20). Tier C = neutral/safe (21).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        literature (Mathew 2021, Tisserand &amp; Young 2014, de Sousa 2015).</t>
+          <t xml:space="preserve">  Tier D = cautioned/avoid (18). Includes mechanism, Theo-specific note, and source.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr"/>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>FLAG — Contains one or more confirmed proconvulsant constituents. For Theo, these</t>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>RISK TIER DEFINITIONS</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       blends require route/dose/timing decisions — not automatic avoidance.</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       Flagged constituents: 1,8-cineole, camphor, thujone, pulegone, eucalyptus</t>
+          <t>CLEAN — No constituents with documented seizure-threshold concern in independent</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">       (E. globulus, E. radiata), rue.</t>
+          <t xml:space="preserve">        literature (Mathew 2021, Tisserand &amp; Young 2014, de Sousa 2015).</t>
         </is>
       </c>
     </row>
@@ -889,110 +957,114 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CONDITIONAL — Chemotype unspecified on label, cannot rule out the proconvulsant</t>
+          <t>FLAG — Contains one or more confirmed proconvulsant constituents. For Theo, these</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">              chemotype. Affects RoseRamie family (RoseRamie, RoseRamie Plus,</t>
+          <t xml:space="preserve">       blends require route/dose/timing decisions — not automatic avoidance.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">              Strength). Recommend contacting AnimalEO to confirm.</t>
+          <t xml:space="preserve">       Flagged constituents: 1,8-cineole, camphor, thujone, pulegone, eucalyptus</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>EVIDENCE FRAMEWORK</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       (E. globulus, E. radiata), rue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CONDITIONAL — Chemotype unspecified on label, cannot rule out the proconvulsant</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Classifications anchored in independent peer-reviewed literature only:</t>
+          <t xml:space="preserve">              chemotype. Affects RoseRamie family (RoseRamie, RoseRamie Plus,</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Mathew T. et al. (2021) Epilepsy Research 173:106626 — 4-yr prospective study,</t>
+          <t xml:space="preserve">              Strength). Recommend contacting AnimalEO to confirm.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    350 seizure cases, 55 essential-oil-related, eucalyptus + camphor implicated</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    across topical, inhalation, and ingestion routes.</t>
+      <c r="A49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>EVIDENCE FRAMEWORK</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Tisserand &amp; Young, Essential Oil Safety 2nd ed (2014).</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • de Sousa et al. (2015) systematic review on anxiolytic/anticonvulsant EO effects.</t>
+          <t>Classifications anchored in independent peer-reviewed literature only:</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Mathew T. et al. (2019) Comment on Bahr 2019 — published critique.</t>
+          <t xml:space="preserve">  • Mathew T. et al. (2021) Epilepsy Research 173:106626 — 4-yr prospective study,</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    350 seizure cases, 55 essential-oil-related, eucalyptus + camphor implicated</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Bahr et al. (2019) is NOT used as a source. Authored by dōTERRA employees</t>
+          <t xml:space="preserve">    across topical, inhalation, and ingestion routes.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>(competing essential oil company), conflict of interest disclosed in the paper itself.</t>
+          <t xml:space="preserve">  • Tisserand &amp; Young, Essential Oil Safety 2nd ed (2014).</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>KEY CORRECTIONS FROM PRIOR ANALYSES (v3, v4)</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • de Sousa et al. (2015) systematic review on anxiolytic/anticonvulsant EO effects.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Mathew T. et al. (2019) Comment on Bahr 2019 — published critique.</t>
         </is>
       </c>
     </row>
@@ -1002,313 +1074,340 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Direct ingredient verification revealed eight ingredient-level errors in the prior</t>
+          <t>Bahr et al. (2019) is NOT used as a source. Authored by dōTERRA employees</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>conversation context. All have been corrected in this dataset:</t>
+          <t>(competing essential oil company), conflict of interest disclosed in the paper itself.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr"/>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>1. NeuroBalance Diffusion Blend — does NOT contain Rosemary, Basil, Peppermint,</t>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>KEY CORRECTIONS FROM PRIOR ANALYSES (v3, v4)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Thyme, Oregano, or Fennel. (Previously misrepresented.)</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Direct ingredient verification revealed eight ingredient-level errors in the prior</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2. NeuroBoost RTU — does NOT contain Rosemary. (Previously had 'rosemary chemotype</t>
+          <t>conversation context. All have been corrected in this dataset:</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   concern' flag — wrong.)</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>1. NeuroBalance Diffusion Blend — does NOT contain Rosemary, Basil, Peppermint,</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>3. Lovely — actually contains Black Pepper + Spearmint + Cabreuva + Lemon Ironbark +</t>
+          <t xml:space="preserve">   Thyme, Oregano, or Fennel. (Previously misrepresented.)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Lavender + Grapefruit. (Previously listed Lavender + Geranium + Ylang Ylang +</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Vetiver — completely wrong blend.)</t>
+          <t>2. NeuroBoost RTU — does NOT contain Rosemary. (Previously had 'rosemary chemotype</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   concern' flag — wrong.)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>4. New Mobility RTU — does NOT contain Wintergreen or Birch. No methyl salicylate.</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Previously flagged for canine salicylate concern — wrong.)</t>
+          <t>3. Lovely — actually contains Black Pepper + Spearmint + Cabreuva + Lemon Ironbark +</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Lavender + Grapefruit. (Previously listed Lavender + Geranium + Ylang Ylang +</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>5. Skin Spray Base — Helichrysum + Frankincense + Copaiba + Lavender + Myrrh.</t>
+          <t xml:space="preserve">   Vetiver — completely wrong blend.)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   No Tea Tree. (Previously listed Tea Tree — wrong.)</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>4. New Mobility RTU — does NOT contain Wintergreen or Birch. No methyl salicylate.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>6. Evict cedarwood — Juniperus mexicana, NOT Cedrus atlantica. Different species,</t>
+          <t xml:space="preserve">   (Previously flagged for canine salicylate concern — wrong.)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   different chemistry.</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>5. Skin Spray Base — Helichrysum + Frankincense + Copaiba + Lavender + Myrrh.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>7. AdrenoBalance and CardioBoost — use Rosemary VERBENONE CT, not Cineole CT.</t>
+          <t xml:space="preserve">   No Tea Tree. (Previously listed Tea Tree — wrong.)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Only LiverBoost contains both chemotypes.</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>6. Evict cedarwood — Juniperus mexicana, NOT Cedrus atlantica. Different species,</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>8. Calm-a-Mile NEAT and RTU — REFORMULATED 2025. Blue Cypress no longer available,</t>
+          <t xml:space="preserve">   different chemistry.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Cabreuva replaces it. New 7-oil formula.</t>
-        </is>
-      </c>
+      <c r="A86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>7. AdrenoBalance and CardioBoost — use Rosemary VERBENONE CT, not Cineole CT.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Also: Dump-a-Lump reformulated Fall 2023 — Blue Cypress → Cabreuva.</t>
+          <t xml:space="preserve">   Only LiverBoost contains both chemotypes.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr"/>
     </row>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t>DR. SHELTON'S DIRECT STATEMENTS (cite-worthy from animaleo.info)</t>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>8. Calm-a-Mile NEAT and RTU — REFORMULATED 2025. Blue Cypress no longer available,</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Cabreuva replaces it. New 7-oil formula.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>On Basil (NeuroBoost product page):</t>
-        </is>
-      </c>
+      <c r="A92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>"Although there have been some cautionary statements in regards to Basil with</t>
+          <t>Also: Dump-a-Lump reformulated Fall 2023 — Blue Cypress → Cabreuva.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>individuals who seizure or have epilepsy, we have not found this to be an issue when</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>used properly. The KittyBoost has been a hallmark treatment for many of our patients,</t>
+      <c r="A94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>DR. SHELTON'S DIRECT STATEMENTS (cite-worthy from animaleo.info)</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>especially those with seizures."</t>
-        </is>
-      </c>
+      <c r="A96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>On Basil (NeuroBoost product page):</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>On Fennel (NeuroBoost product page):</t>
+          <t>"Although there have been some cautionary statements in regards to Basil with</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>"Occasionally Fennel is reported as needing to be avoided for those with seizures —</t>
+          <t>individuals who seizure or have epilepsy, we have not found this to be an issue when</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>however clinically we have not found this to be true. Also within Tisserand's most</t>
+          <t>used properly. The KittyBoost has been a hallmark treatment for many of our patients,</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>current book Essential Oil Safety — there is little cause for concern for fennel oil</t>
+          <t>especially those with seizures."</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>to have convulsant activity."</t>
-        </is>
-      </c>
+      <c r="A102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>OPEN QUESTION FOR ANIMALEO</t>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>On Fennel (NeuroBoost product page):</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>"Occasionally Fennel is reported as needing to be avoided for those with seizures —</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr"/>
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>however clinically we have not found this to be true. Also within Tisserand's most</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>RoseRamie's official ingredient list specifies 'Rosemary (Rosmarinus officinalis)'</t>
+          <t>current book Essential Oil Safety — there is little cause for concern for fennel oil</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>WITHOUT a chemotype designation. Every other AnimalEO blend specifies the chemotype</t>
+          <t>to have convulsant activity."</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>(LiverBoost, AdrenoBalance, CardioBoost, UroBoost, Open-Air, Evict, EIEIO EO,</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>YeastyBeasty, Focus, Oust). Recommend emailing the company to confirm whether the</t>
+      <c r="A108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>OPEN QUESTION FOR ANIMALEO</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>rosemary in RoseRamie is the verbenone CT (neutral) or cineole CT (proconvulsant).</t>
-        </is>
-      </c>
+      <c r="A110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>This question affects three blends through inheritance: RoseRamie, RoseRamie Plus,</t>
+          <t>RoseRamie's official ingredient list specifies 'Rosemary (Rosmarinus officinalis)'</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>WITHOUT a chemotype designation. Every other AnimalEO blend specifies the chemotype</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>(LiverBoost, AdrenoBalance, CardioBoost, UroBoost, Open-Air, Evict, EIEIO EO,</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>YeastyBeasty, Focus, Oust). Recommend emailing the company to confirm whether the</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>rosemary in RoseRamie is the verbenone CT (neutral) or cineole CT (proconvulsant).</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>This question affects three blends through inheritance: RoseRamie, RoseRamie Plus,</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>and Strength.</t>
         </is>
@@ -32419,4 +32518,2302 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>ANIMALEO SINGLE OILS — ACTIVE-SEIZURE USE TIERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>All 69 AnimalEO single oils, classified for active-seizure use (post-ictal + cluster-window). Phase 1 evidence triage, May 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>COVERAGE FINDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Theo's Clean-tier blends already contain ALL 10 Tier A oils and 17 of 20 Tier B oils. NeuroBalance Diffusion alone contains every Tier A oil — the single most evidence-rich product in the AnimalEO catalog. Strongest individual rescue candidates by mechanism: Frankincense (anti-neuroinflammatory, multiple rat models) and Copaiba (β-caryophyllene CB2 agonist, intranasal nanoemulsion tested for seizures).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>In Clean Blend?</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Evidence / Mechanism</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Theo-Specific Note</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Key Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Balsam Fir</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>α-pinene + β-pinene anticonvulsant in animal models</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance. Shelton first-line rec.</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>de Sousa 2015 review</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>Copaiba</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>β-caryophyllene CB2 agonist; MES-protective at 30 mg/kg comparable to phenytoin; intranasal nanoemulsion tested for PTZ</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance + Calm-a-Mile. CB2 mechanism non-overlapping with Theo's CBD. Strong rescue candidate.</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="inlineStr">
+        <is>
+          <t>Tchekalarova 2018, 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Frankincense</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>Multiple rat models — pilocarpine, penicillin, PTZ-kindling. β-boswellic acid 90% PTZ reduction. NF-κB suppression.</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance + Calm-a-Mile. Reasonable for emergency inhalation. No documented AED/CBD interaction.</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>Goyal 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>German Chamomile</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="inlineStr">
+        <is>
+          <t>α-bisabolol GABA-A activity; chamazulene anti-inflammatory</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance. Very safe profile.</t>
+        </is>
+      </c>
+      <c r="F11" s="35" t="inlineStr">
+        <is>
+          <t>Brazilian review</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Helichrysum</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
+        <is>
+          <t>No direct seizure model; clinical use in canine seizure protocols. Anti-inflammatory + neuroregenerative.</t>
+        </is>
+      </c>
+      <c r="E12" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance. Clinical-use evidence only; weaker than other Tier A.</t>
+        </is>
+      </c>
+      <c r="F12" s="35" t="inlineStr">
+        <is>
+          <t>Shelton ADR-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Laurus nobilis</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>Tisserand 2014 explicitly cites as anticonvulsant despite 40.8% cineole. Counterpoint to 'cineole=proconvulsant'.</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance. Defensible despite cineole; OK to skip if continuing eucalyptus avoidance.</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>Sayyah 2002a; Tisserand 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" s="35" t="inlineStr">
+        <is>
+          <t>Linalool NMDA antagonism + GABA-A agonism. Koutroumanidou 2013 PTZ-latency increase. Birmingham clinical use.</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance + Calm-a-Mile. Inhalation route validated.</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>Koutroumanidou 2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>Citral, citronellal, β-caryophyllene. PTZ+MES anticonvulsant; 4-AP brain slice ictal-like discharge blockade. VGSC blocker.</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance. Mechanism complements levetiracetam (different target). Strong rescue candidate.</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>Chindo 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Roman Chamomile</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Esters + α-pinene; α-pinene anticonvulsant. Birmingham clinical aromatherapy protocols.</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance + Calm-a-Mile. Often inhaled directly during seizures clinically.</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Birmingham clinical study</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>Valerian</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>Valerenic acid GABA-A potentiation; PTZ + MES anticonvulsant in rodents; zebrafish PTZ delay. GABAzine antagonism confirms mechanism.</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>In NeuroBalance. CAUTION: documented additive sedation with benzos (midazolam) — feature during rescue, but worth noting.</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>PTZ + MES rodent models</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Bergamot Full</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Anxiolytic, anti-allodynic. Sakurada 2009 antinociceptive.</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>Photosensitizing on skin — prefer BF version for topical.</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Sakurada 2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Bergamot BF</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Bergapten-free; anxiolytic without photosensitization.</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>Better choice for topical. Same anxiolytic effect as Full.</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>Clinical EO research</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Black Pepper</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>β-caryophyllene source (~30%) — CB2 modulation; lower BCP concentration than Copaiba.</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>Tier-A-by-association via BCP. In Clean blends.</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>Tchekalarova 2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Clary Sage</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>Linalyl acetate + linalool; anxiolytic, GABA-A modulation. Different from Salvia officinalis (sage thujones).</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>NOT the same as common sage — safe for Theo. Linalool-class.</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Linalool literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Geranium Bourbon</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Citronellol + geraniol; anxiolytic, balancing. Some PTZ data for citronellol.</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>Calming; safe profile.</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>PTZ animal models</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Grapefruit Pink</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>Limonene 88-95%; mood, mild calming. Limonene weak anticonvulsant.</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>CYP3A4 inhibitor (grapefruit family) — concern with Theo's clorazepate/midazolam rescue meds. Use with timing care.</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>Limonene reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Ledum</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>No ⚪</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>Liver detox, calming. Limited research; traditional 'emotional release' use.</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>NOT in any Clean blend. Buy as single only if TCVM vet specifically indicates.</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>Traditional use only</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>Limonene; mood, calming. Lower CYP3A4 concern than grapefruit.</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>Safer limonene-class option.</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>Limonene reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Marjoram</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Terpinen-4-ol + sabinene hydrate; sedative, antispasmodic. Often paired with lavender.</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>Calming; safe profile.</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>EO clinical literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Neroli</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>No ⚪</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Linalool + limonene; strong calming reputation. Limited direct seizure data.</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>NOT in any Clean blend. Buy as single only if TCVM vet specifically indicates.</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>Linalool literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Orange Sweet</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Limonene 90%+; mood, mild calming.</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>Gentle anxiolytic.</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>Limonene reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Orange Wild</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Bitter orange variant; same limonene profile.</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Gentle anxiolytic.</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>Limonene reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Palmarosa</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Geraniol; calming, balancing. Geraniol some animal-model anticonvulsant data.</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>Safe profile; could trend Tier A by constituent.</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>de Sousa 2015 review</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Patchouli Dark Aged</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>Patchoulol + sesquiterpenes; grounding, anti-anxiety.</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>Limited direct seizure data; calming use.</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>Sesquiterpene literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Rose Otto</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Citronellol + geraniol; emotional balance, anxiolytic.</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>Often used in canine seizure-anxiety protocols.</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>EO clinical literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Sandalwood</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>Santalols; sedative, anxiolytic. Santalol has some CNS activity.</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Calming reputation.</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>Santalol literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Tangerine</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>Limonene; mood, mild calming.</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>Same as Sweet Orange.</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>Limonene reviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Vetiver</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Vetiverol + khusimol; sedating, grounding. Strong anxiolytic per Pranjic 2023.</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>In NeuroBalance. The 'heaviest' calming oil.</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>Pranjic 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Vitex (Chaste Tree Berry)</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="inlineStr">
+        <is>
+          <t>No ⚪</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>Hormonal balance, sedative. Limited seizure data.</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>NOT in any Clean blend. Buy as single only if TCVM vet specifically indicates.</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>Hormonal literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Ylang Ylang</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Linalool + geranyl acetate; anxiolytic, calming. Birmingham clinical use; Epilepsy Society UK calming oils list.</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
+        <is>
+          <t>In NeuroBalance. Clinical-use evidence.</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="inlineStr">
+        <is>
+          <t>Birmingham study</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="36" t="inlineStr">
+        <is>
+          <t>Black Cumin</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="39" t="inlineStr">
+        <is>
+          <t>Some anticonvulsant data (thymoquinone) but variable; Tier B/C boundary.</t>
+        </is>
+      </c>
+      <c r="E38" s="39" t="inlineStr">
+        <is>
+          <t>Safe but not seizure-targeted.</t>
+        </is>
+      </c>
+      <c r="F38" s="39" t="inlineStr">
+        <is>
+          <t>Thymoquinone literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="36" t="inlineStr">
+        <is>
+          <t>Cedarwood Atlas</t>
+        </is>
+      </c>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C39" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="39" t="inlineStr">
+        <is>
+          <t>Calming; no direct seizure data. (Not the same as caution-warning 'cedar' oils.)</t>
+        </is>
+      </c>
+      <c r="E39" s="39" t="inlineStr">
+        <is>
+          <t>Safe; calming.</t>
+        </is>
+      </c>
+      <c r="F39" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="36" t="inlineStr">
+        <is>
+          <t>Cilantro</t>
+        </is>
+      </c>
+      <c r="B40" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C40" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="39" t="inlineStr">
+        <is>
+          <t>Detox; no seizure data.</t>
+        </is>
+      </c>
+      <c r="E40" s="39" t="inlineStr">
+        <is>
+          <t>Safe; not relevant.</t>
+        </is>
+      </c>
+      <c r="F40" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="36" t="inlineStr">
+        <is>
+          <t>Cistus</t>
+        </is>
+      </c>
+      <c r="B41" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C41" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="39" t="inlineStr">
+        <is>
+          <t>Anti-inflammatory; no seizure data.</t>
+        </is>
+      </c>
+      <c r="E41" s="39" t="inlineStr">
+        <is>
+          <t>Safe; not relevant.</t>
+        </is>
+      </c>
+      <c r="F41" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="36" t="inlineStr">
+        <is>
+          <t>Citronella</t>
+        </is>
+      </c>
+      <c r="B42" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C42" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="39" t="inlineStr">
+        <is>
+          <t>Insect repellent; citronellal has weak anticonvulsant data.</t>
+        </is>
+      </c>
+      <c r="E42" s="39" t="inlineStr">
+        <is>
+          <t>Safe; not seizure-targeted.</t>
+        </is>
+      </c>
+      <c r="F42" s="39" t="inlineStr">
+        <is>
+          <t>Weak citronellal data</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="36" t="inlineStr">
+        <is>
+          <t>Cypress</t>
+        </is>
+      </c>
+      <c r="B43" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C43" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="39" t="inlineStr">
+        <is>
+          <t>Circulatory; no seizure data.</t>
+        </is>
+      </c>
+      <c r="E43" s="39" t="inlineStr">
+        <is>
+          <t>Safe; not relevant.</t>
+        </is>
+      </c>
+      <c r="F43" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="36" t="inlineStr">
+        <is>
+          <t>Dill Weed</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C44" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="39" t="inlineStr">
+        <is>
+          <t>Carvone — actually anticonvulsant per Brazilian review; could be Tier A by constituent.</t>
+        </is>
+      </c>
+      <c r="E44" s="39" t="inlineStr">
+        <is>
+          <t>Borderline Tier A; defensible reclassification later.</t>
+        </is>
+      </c>
+      <c r="F44" s="39" t="inlineStr">
+        <is>
+          <t>de Sousa 2015 review</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="36" t="inlineStr">
+        <is>
+          <t>Ginger</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C45" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="39" t="inlineStr">
+        <is>
+          <t>Digestive; anti-nausea (post-ictal nausea support).</t>
+        </is>
+      </c>
+      <c r="E45" s="39" t="inlineStr">
+        <is>
+          <t>Useful for post-ictal nausea; safe.</t>
+        </is>
+      </c>
+      <c r="F45" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="36" t="inlineStr">
+        <is>
+          <t>Juniper Berry</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C46" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="39" t="inlineStr">
+        <is>
+          <t>Diuretic; safe profile. Shelton lists it.</t>
+        </is>
+      </c>
+      <c r="E46" s="39" t="inlineStr">
+        <is>
+          <t>Safe; not seizure-targeted.</t>
+        </is>
+      </c>
+      <c r="F46" s="39" t="inlineStr">
+        <is>
+          <t>Shelton ADR-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="36" t="inlineStr">
+        <is>
+          <t>Lemon Eucalyptus</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C47" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D47" s="39" t="inlineStr">
+        <is>
+          <t>Citronellal-dominant; NOT same as Eucalyptus despite name — much safer.</t>
+        </is>
+      </c>
+      <c r="E47" s="39" t="inlineStr">
+        <is>
+          <t>Despite the name, NOT in the eucalyptus caution group.</t>
+        </is>
+      </c>
+      <c r="F47" s="39" t="inlineStr">
+        <is>
+          <t>Constituent profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="36" t="inlineStr">
+        <is>
+          <t>Lime Cold Pressed</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C48" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="39" t="inlineStr">
+        <is>
+          <t>Limonene; photosensitizing.</t>
+        </is>
+      </c>
+      <c r="E48" s="39" t="inlineStr">
+        <is>
+          <t>Safe but photosensitizing; prefer SD version for topical.</t>
+        </is>
+      </c>
+      <c r="F48" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="36" t="inlineStr">
+        <is>
+          <t>Lime Steam Distilled</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C49" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D49" s="39" t="inlineStr">
+        <is>
+          <t>Limonene; non-photosensitizing.</t>
+        </is>
+      </c>
+      <c r="E49" s="39" t="inlineStr">
+        <is>
+          <t>Safer for topical use.</t>
+        </is>
+      </c>
+      <c r="F49" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="36" t="inlineStr">
+        <is>
+          <t>May Chang</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C50" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D50" s="39" t="inlineStr">
+        <is>
+          <t>Citral; calming, mild anticonvulsant.</t>
+        </is>
+      </c>
+      <c r="E50" s="39" t="inlineStr">
+        <is>
+          <t>Borderline B; calming use.</t>
+        </is>
+      </c>
+      <c r="F50" s="39" t="inlineStr">
+        <is>
+          <t>Citral literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="36" t="inlineStr">
+        <is>
+          <t>Melaleuca alternifolia (Tea Tree)</t>
+        </is>
+      </c>
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C51" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D51" s="39" t="inlineStr">
+        <is>
+          <t>Antimicrobial; NOT cineole-dominant, safe.</t>
+        </is>
+      </c>
+      <c r="E51" s="39" t="inlineStr">
+        <is>
+          <t>Despite tea-tree class, low cineole; safe.</t>
+        </is>
+      </c>
+      <c r="F51" s="39" t="inlineStr">
+        <is>
+          <t>Constituent profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="36" t="inlineStr">
+        <is>
+          <t>Myrrh</t>
+        </is>
+      </c>
+      <c r="B52" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C52" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D52" s="39" t="inlineStr">
+        <is>
+          <t>Anti-inflammatory; no seizure data.</t>
+        </is>
+      </c>
+      <c r="E52" s="39" t="inlineStr">
+        <is>
+          <t>Safe; not relevant.</t>
+        </is>
+      </c>
+      <c r="F52" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
+          <t>Myrtle</t>
+        </is>
+      </c>
+      <c r="B53" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C53" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D53" s="39" t="inlineStr">
+        <is>
+          <t>Mild oil; similar to tea-tree class.</t>
+        </is>
+      </c>
+      <c r="E53" s="39" t="inlineStr">
+        <is>
+          <t>Safe; not seizure-targeted.</t>
+        </is>
+      </c>
+      <c r="F53" s="39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>Plai</t>
+        </is>
+      </c>
+      <c r="B54" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C54" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D54" s="39" t="inlineStr">
+        <is>
+          <t>Anti-inflammatory, neuroprotective in LPS model. Camphoraceous smell — verify chemotype.</t>
+        </is>
+      </c>
+      <c r="E54" s="39" t="inlineStr">
+        <is>
+          <t>Verify camphor content with supplier before using.</t>
+        </is>
+      </c>
+      <c r="F54" s="39" t="inlineStr">
+        <is>
+          <t>LPS neuroprotection model</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="36" t="inlineStr">
+        <is>
+          <t>Saro (Mandravasarotra)</t>
+        </is>
+      </c>
+      <c r="B55" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C55" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D55" s="39" t="inlineStr">
+        <is>
+          <t>Cineole-bearing — likely belongs in Tier D if ≥40% cineole. Verify chemotype.</t>
+        </is>
+      </c>
+      <c r="E55" s="39" t="inlineStr">
+        <is>
+          <t>Verify chemotype; potential reclassification to Tier D.</t>
+        </is>
+      </c>
+      <c r="F55" s="39" t="inlineStr">
+        <is>
+          <t>Constituent profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="36" t="inlineStr">
+        <is>
+          <t>Spearmint</t>
+        </is>
+      </c>
+      <c r="B56" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C56" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D56" s="39" t="inlineStr">
+        <is>
+          <t>Carvone-rich; carvone has anticonvulsant data per systematic review. Could be Tier A.</t>
+        </is>
+      </c>
+      <c r="E56" s="39" t="inlineStr">
+        <is>
+          <t>Borderline Tier A; defensible reclassification.</t>
+        </is>
+      </c>
+      <c r="F56" s="39" t="inlineStr">
+        <is>
+          <t>de Sousa 2015 review</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="36" t="inlineStr">
+        <is>
+          <t>Spruce Black</t>
+        </is>
+      </c>
+      <c r="B57" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C57" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D57" s="39" t="inlineStr">
+        <is>
+          <t>Pinene-rich; similar profile to Balsam Fir.</t>
+        </is>
+      </c>
+      <c r="E57" s="39" t="inlineStr">
+        <is>
+          <t>Could trend Tier A by α-pinene.</t>
+        </is>
+      </c>
+      <c r="F57" s="39" t="inlineStr">
+        <is>
+          <t>Pinene literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="36" t="inlineStr">
+        <is>
+          <t>Western Red Cedar</t>
+        </is>
+      </c>
+      <c r="B58" s="37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C58" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D58" s="39" t="inlineStr">
+        <is>
+          <t>May contain thujone-like compounds depending on source. Verify chemotype.</t>
+        </is>
+      </c>
+      <c r="E58" s="39" t="inlineStr">
+        <is>
+          <t>Verify chemotype; potential reclassification to Tier D.</t>
+        </is>
+      </c>
+      <c r="F58" s="39" t="inlineStr">
+        <is>
+          <t>Constituent profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>Anise</t>
+        </is>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C59" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D59" s="21" t="inlineStr">
+        <is>
+          <t>Anethole + fenchone — same class as fennel. Same UGT/CYP3A4 concern. Not direct convulsant per Tisserand.</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>Same family as fennel; same caveat. Avoid for active seizure use.</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>Tisserand 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>Basil Sweet</t>
+        </is>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D60" s="21" t="inlineStr">
+        <is>
+          <t>Estragole/methyl chavicol concern at high doses. Shelton uses it but flags caution. Not direct convulsant.</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="inlineStr">
+        <is>
+          <t>On Shelton's caution list. Avoid during active-seizure window.</t>
+        </is>
+      </c>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t>Shelton ADR-II caution list</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>Cassia</t>
+        </is>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D61" s="21" t="inlineStr">
+        <is>
+          <t>Cinnamaldehyde at high concentrations CNS-stimulant. Hot oil. Tisserand 2014 caution.</t>
+        </is>
+      </c>
+      <c r="E61" s="21" t="inlineStr">
+        <is>
+          <t>Avoid during active-seizure window.</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="inlineStr">
+        <is>
+          <t>Tisserand 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>Catnip ⚠</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D62" s="21" t="inlineStr">
+        <is>
+          <t>Aydin 1996 mouse study — dietary 10% increased picrotoxin/strychnine seizure susceptibility. Single source, dietary route. Shelton uses in 12 formulas; not on her caution list. Tisserand does not list as proconvulsant.</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="inlineStr">
+        <is>
+          <t>Borderline. Dataset is NOT reclassified — see Catnip discussion in Evidence appendix. Topical/diffusion route at 1-3% likely doesn't replicate Aydin findings.</t>
+        </is>
+      </c>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t>Aydin 1996</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>Cinnamon Bark</t>
+        </is>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D63" s="21" t="inlineStr">
+        <is>
+          <t>Cinnamaldehyde, hot oil, dermal irritant. CNS-stimulant at dose.</t>
+        </is>
+      </c>
+      <c r="E63" s="21" t="inlineStr">
+        <is>
+          <t>Avoid during active-seizure window.</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
+          <t>Tisserand 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>Cinnamon Leaf</t>
+        </is>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="inlineStr">
+        <is>
+          <t>Eugenol IS anticonvulsant per Brazilian review. Caution is dermal irritation, not seizure mechanism. Borderline reclassification to Tier A.</t>
+        </is>
+      </c>
+      <c r="E64" s="21" t="inlineStr">
+        <is>
+          <t>Could be Tier A for inhalation use. Currently flagged for hot-oil concerns, not seizure mechanism.</t>
+        </is>
+      </c>
+      <c r="F64" s="21" t="inlineStr">
+        <is>
+          <t>de Sousa 2015 review</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>Clove Bud</t>
+        </is>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D65" s="21" t="inlineStr">
+        <is>
+          <t>Eugenol 75-90% — IS anticonvulsant per Brazilian review. Hot oil + dermal irritation. Borderline Tier A by mechanism.</t>
+        </is>
+      </c>
+      <c r="E65" s="21" t="inlineStr">
+        <is>
+          <t>Could be Tier A for inhalation use. Currently flagged for hot-oil concerns, not seizure mechanism.</t>
+        </is>
+      </c>
+      <c r="F65" s="21" t="inlineStr">
+        <is>
+          <t>de Sousa 2015 review</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>Eucalyptus globulus</t>
+        </is>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D66" s="21" t="inlineStr">
+        <is>
+          <t>v5.0 Conditional. Mathew 2021 prospective data implicates eucalyptus.</t>
+        </is>
+      </c>
+      <c r="E66" s="21" t="inlineStr">
+        <is>
+          <t>Continue avoiding per Theo's existing practice and v5.0 framework.</t>
+        </is>
+      </c>
+      <c r="F66" s="21" t="inlineStr">
+        <is>
+          <t>Mathew 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>Fennel Sweet</t>
+        </is>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D67" s="21" t="inlineStr">
+        <is>
+          <t>v5.0 Fennel-Conditional. Pharmacokinetic concern (CYP3A4 + UGT inhibition). Already in NeuroBoost.</t>
+        </is>
+      </c>
+      <c r="E67" s="21" t="inlineStr">
+        <is>
+          <t>Pharmacokinetic timing matters on storm days for clorazepate/midazolam.</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
+        <is>
+          <t>Tisserand 2014; Skalli 2011</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>Hyssop</t>
+        </is>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D68" s="21" t="inlineStr">
+        <is>
+          <t>PROCONVULSANT — pinocamphone. Tisserand Table 10.1. Shelton caution list.</t>
+        </is>
+      </c>
+      <c r="E68" s="21" t="inlineStr">
+        <is>
+          <t>AVOID. Strong contraindication.</t>
+        </is>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t>Tisserand 2014 Table 10.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>Lemongrass</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D69" s="21" t="inlineStr">
+        <is>
+          <t>Citral IS anticonvulsant per multiple animal models. Should be Tier A. Currently in D for hot-oil concerns only.</t>
+        </is>
+      </c>
+      <c r="E69" s="21" t="inlineStr">
+        <is>
+          <t>Defensible reclassification to Tier A for inhalation/diffusion use.</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
+          <t>Citral animal models</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>Nutmeg</t>
+        </is>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="21" t="inlineStr">
+        <is>
+          <t>Myristicin — psychoactive at high doses. Variable convulsant potential.</t>
+        </is>
+      </c>
+      <c r="E70" s="21" t="inlineStr">
+        <is>
+          <t>Avoid during active-seizure window.</t>
+        </is>
+      </c>
+      <c r="F70" s="21" t="inlineStr">
+        <is>
+          <t>Myristicin literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>Oregano</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" s="21" t="inlineStr">
+        <is>
+          <t>Carvacrol/thymol — hot oil, dermal irritant. Some carvacrol anticonvulsant data but not used in seizure protocols.</t>
+        </is>
+      </c>
+      <c r="E71" s="21" t="inlineStr">
+        <is>
+          <t>Avoid during active-seizure window.</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
+        <is>
+          <t>Hot oil class</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>Peppermint</t>
+        </is>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" s="21" t="inlineStr">
+        <is>
+          <t>Mixed: weak proconvulsant in some studies, GABA potentiator in others. Koutroumanidou 2013 showed 100% PTZ survival. Tisserand notes use cautiously in epilepsy.</t>
+        </is>
+      </c>
+      <c r="E72" s="21" t="inlineStr">
+        <is>
+          <t>Mixed evidence. Some sources avoid; others permissive. Your call with TCVM vet.</t>
+        </is>
+      </c>
+      <c r="F72" s="21" t="inlineStr">
+        <is>
+          <t>Koutroumanidou 2013; Tisserand 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>Rosemary Cineole</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D73" s="21" t="inlineStr">
+        <is>
+          <t>v5.0 Conditional. Cineole concern.</t>
+        </is>
+      </c>
+      <c r="E73" s="21" t="inlineStr">
+        <is>
+          <t>Continue avoiding per v5.0 framework.</t>
+        </is>
+      </c>
+      <c r="F73" s="21" t="inlineStr">
+        <is>
+          <t>Tisserand 2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>Rue</t>
+        </is>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D74" s="21" t="inlineStr">
+        <is>
+          <t>v5.0 FLAG. Documented neurotoxicity.</t>
+        </is>
+      </c>
+      <c r="E74" s="21" t="inlineStr">
+        <is>
+          <t>AVOID. Strong contraindication.</t>
+        </is>
+      </c>
+      <c r="F74" s="21" t="inlineStr">
+        <is>
+          <t>Tisserand 2014; Shelton ADR-II</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>Tarragon</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D75" s="21" t="inlineStr">
+        <is>
+          <t>Estragole-dominant. Shelton caution list.</t>
+        </is>
+      </c>
+      <c r="E75" s="21" t="inlineStr">
+        <is>
+          <t>AVOID per Shelton's own protocol.</t>
+        </is>
+      </c>
+      <c r="F75" s="21" t="inlineStr">
+        <is>
+          <t>Shelton ADR-II caution list</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>Thyme Thymol</t>
+        </is>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>Phenolic, hot oil. Some carvacrol-like data; primarily caution oil for sensitive patients.</t>
+        </is>
+      </c>
+      <c r="E76" s="21" t="inlineStr">
+        <is>
+          <t>Avoid during active-seizure window.</t>
+        </is>
+      </c>
+      <c r="F76" s="21" t="inlineStr">
+        <is>
+          <t>Hot oil class</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/animaleo_theo_dataset.xlsx
+++ b/animaleo_theo_dataset.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,8 +75,12 @@
       <color rgb="002E75B6"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +127,16 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE0BC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D4B8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -150,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -262,6 +276,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -712,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A117"/>
+  <dimension ref="A1:A152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1410,6 +1432,223 @@
       <c r="A117" s="2" t="inlineStr">
         <is>
           <t>and Strength.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="40">
+        <f>== v5.2 UPDATE (May 2026) ===</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="41" t="inlineStr">
+        <is>
+          <t>v5.2 introduces two new precautionary tiers:</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • OREGANO-CONDITIONAL (2 blends): AromaBoost #1 (RTU), Dump-a-Lump</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • FENNEL+OREGANO-CONDITIONAL (6 blends): Boost in a Bottle, KittyBoost, KittyBoost LITE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      NeuroBoost RTU, SugarBalance, ThyroBalance</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="41" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="41" t="inlineStr">
+        <is>
+          <t>Rationale: canine-specific oregano evidence is thin in BOTH directions. No published canine</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="41" t="inlineStr">
+        <is>
+          <t>case series equivalent to Khan/McLean/Slater 2014 JAVMA tea tree paper (443 cases) exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="41" t="inlineStr">
+        <is>
+          <t>for oregano. Peer-reviewed canine USE exists (Fereydooni 2023 Open Vet J: 5% topical</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="41" t="inlineStr">
+        <is>
+          <t>carvacrol for demodicosis). The widely-cited pet-blog claim that dogs lack glucuronidation</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="41" t="inlineStr">
+        <is>
+          <t>for phenols is factually wrong (Merck Vet Manual, Savides 1980, Court 2013) — that's a</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="41" t="inlineStr">
+        <is>
+          <t>cat-specific characteristic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="41" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="41" t="inlineStr">
+        <is>
+          <t>These tiers reflect precautionary case-by-case use, not hard avoid. Single oregano EO</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="41" t="inlineStr">
+        <is>
+          <t>remains AVOID. NeuroBoost RTU remains in Theo's active rotation with both flags acknowledged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="41" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="41" t="inlineStr">
+        <is>
+          <t>Framework note: classification is independent of Bahr 2019 (excluded for COI). Anchors are</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="41" t="inlineStr">
+        <is>
+          <t>Tisserand &amp; Young 2014, Shelton ADR-II, Mathew 2021, Royce 2024, Merck Vet Manual,</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="41" t="inlineStr">
+        <is>
+          <t>Khan et al 2014 JAVMA, Manville 2014, Fereydooni 2023, and independent canine pharmacology.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="41" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="41" t="inlineStr">
+        <is>
+          <t>ORDERING within each tier:</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • CLEAN tier — retains its v5.1 clinical sub-tier structure in the HTML index:</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Tier 1 · Seizure-Indicated (NeuroBalance Diffusion Blend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Tier 2 · Calming &amp; Adjunct (Hormone Blend, Calm-a-Mile, Smooth Delivery, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Tier 4 · General Wellness (Sunshine in a Bottle, Lovely, Charming)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Tier 5 · Specific-Purpose (Feathered, Lime-a-Mint, Any-Itis, AromaBoost variants, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      (Tier 3 · Body-System Support is empty — all body-system blends are CONDITIONAL or</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       FENNEL+OREGANO-CONDITIONAL in v5.2 and thus not in CLEAN.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Within each sub-tier, blends are ordered by ANTI-CONVULSANT CONSTITUENT RATIO (descending).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • All other tiers (OREGANO-CONDITIONAL, FENNEL+OREGANO-CONDITIONAL, FENNEL-CONDITIONAL,</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      CONDITIONAL, FLAG) — flat ordering by anti-convulsant ratio (descending).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="41" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="41" t="inlineStr">
+        <is>
+          <t>The Excel file stores only the top-level tier assignment per blend. The CLEAN sub-tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="41" t="inlineStr">
+        <is>
+          <t>structure lives in the HTML index only.</t>
         </is>
       </c>
     </row>
@@ -1751,9 +1990,9 @@
           <t>AromaBoost #1 (RTU)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>CLEAN</t>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -2048,7 +2287,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -2090,7 +2329,7 @@
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>5-oil insect/odor blend. E. citriodora is citronellal-dominant (low cineole). Lemon Tea Tree (Leptospermum petersonii) is citral-dominant. Clean profile.</t>
+          <t>⚠ CONDITIONAL (reclassified from CLEAN). 5-oil insect/odor blend. E. citriodora is citronellal-dominant (low cineole) and Lemon Tea Tree (Leptospermum petersonii) is citral-dominant — both have favorable rodent seizure-mechanism profiles. RECLASSIFIED due to Citronella content: ASPCA, Pet Poison Helpline, and VCA Animal Hospitals document neurological symptoms in dogs from concentrated citronella EO exposure, with grooming/licking after topical application as the practical concern. For Theo's epilepsy protocol, this canine-clinical caution takes precedence over the favorable rodent anticonvulsant data on citronellal.</t>
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr">
@@ -2105,9 +2344,9 @@
           <t>Boost in a Bottle</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-CONDITIONAL</t>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -2166,7 +2405,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -2208,7 +2447,7 @@
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>7-oil cleaning blend. Cilantro + citrus-led. Tea Tree (M. alternifolia) present.</t>
+          <t>⚠ CONDITIONAL (reclassified from CLEAN). Cleaning blend (surfaces, not for direct application to Theo). RECLASSIFIED due to Citronella content for framework consistency: ASPCA, Pet Poison Helpline, and VCA Animal Hospitals document neurological symptoms in dogs from concentrated citronella EO exposure. The cleaning-blend context lowers but doesn't eliminate Theo's exposure (residual contact, inhalation of cleaning vapor). Framework treats citronella consistently across all blends regardless of labeled use.</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr">
@@ -2695,9 +2934,9 @@
           <t>Dump-a-Lump</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>CLEAN</t>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -3285,9 +3524,9 @@
           <t>KittyBoost</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-CONDITIONAL</t>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
@@ -3344,9 +3583,9 @@
           <t>KittyBoost LITE</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-CONDITIONAL</t>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
@@ -3698,9 +3937,9 @@
           <t>NeuroBoost RTU</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-CONDITIONAL</t>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C39" s="16" t="inlineStr">
@@ -3742,7 +3981,7 @@
       </c>
       <c r="L39" s="17" t="inlineStr">
         <is>
-          <t>KittyBoost + NeuroBalance oils. NO ROSEMARY. Shelton page: 'Basil... we have not found this to be an issue when used properly. KittyBoost has been hallmark treatment for seizure patients.'</t>
+          <t>KittyBoost + NeuroBalance oils. NO ROSEMARY. Shelton page: 'Basil... we have not found this to be an issue when used properly. KittyBoost has been hallmark treatment for seizure patients.' ADDITIONAL CANINE-CLINICAL CONCERN: contains Citronella. Per ASPCA, Pet Poison Helpline, and VCA Animal Hospitals, citronella EO carries a canine-specific caution due to documented neurological adverse reactions (tremors, CNS depression, convulsions in severe cases). Topical application raises the grooming/licking exposure route. Rationale for Conditional status now multi-factor: Fennel (pharmacokinetic concern) AND Citronella (canine-clinical caution).</t>
         </is>
       </c>
       <c r="M39" s="17" t="inlineStr">
@@ -4229,9 +4468,9 @@
           <t>SugarBalance</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-CONDITIONAL</t>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
@@ -4347,9 +4586,9 @@
           <t>ThyroBalance</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-CONDITIONAL</t>
+      <c r="B50" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -6379,7 +6618,7 @@
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>NEUTRAL for seizure mechanism (Tisserand 2014 Ch 10: Java citronella oil, 27.4% citronellal + 10.5% citronellol, inhibited PTZ, PIC and strychnine-induced convulsions in rodent models). CANINE-SPECIFIC CAUTION: ASPCA Animal Poison Control and Pet Poison Helpline document neurological symptoms (tremors, CNS depression, convulsions in severe cases) from concentrated citronella EO exposure in dogs. VCA Animal Hospitals lists citronella in canine essential-oil poisoning category. Grooming/licking after topical application is the practical route of concern. For an epileptic dog, the precautionary stance is to avoid concentrated citronella exposure regardless of favorable rodent mechanism data.</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -6392,7 +6631,7 @@
       </c>
       <c r="E67" s="23" t="inlineStr">
         <is>
-          <t>No published seizure-threshold concern</t>
+          <t>Tisserand &amp; Young 2014 (rodent PTZ anticonvulsant); ASPCA Animal Poison Control; Pet Poison Helpline; VCA Animal Hospitals (canine clinical toxicity)</t>
         </is>
       </c>
     </row>
@@ -8961,7 +9200,7 @@
       </c>
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
@@ -9003,7 +9242,7 @@
       </c>
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
@@ -9045,7 +9284,7 @@
       </c>
       <c r="B43" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
@@ -9927,7 +10166,7 @@
       </c>
       <c r="B64" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C64" s="27" t="inlineStr">
@@ -9969,7 +10208,7 @@
       </c>
       <c r="B65" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C65" s="27" t="inlineStr">
@@ -10011,7 +10250,7 @@
       </c>
       <c r="B66" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C66" s="27" t="inlineStr">
@@ -10053,7 +10292,7 @@
       </c>
       <c r="B67" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C67" s="27" t="inlineStr">
@@ -10095,7 +10334,7 @@
       </c>
       <c r="B68" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C68" s="27" t="inlineStr">
@@ -10137,7 +10376,7 @@
       </c>
       <c r="B69" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C69" s="27" t="inlineStr">
@@ -10179,7 +10418,7 @@
       </c>
       <c r="B70" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C70" s="27" t="inlineStr">
@@ -10221,7 +10460,7 @@
       </c>
       <c r="B71" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C71" s="27" t="inlineStr">
@@ -10263,7 +10502,7 @@
       </c>
       <c r="B72" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C72" s="27" t="inlineStr">
@@ -10305,7 +10544,7 @@
       </c>
       <c r="B73" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C73" s="27" t="inlineStr">
@@ -10347,7 +10586,7 @@
       </c>
       <c r="B74" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C74" s="27" t="inlineStr">
@@ -10389,7 +10628,7 @@
       </c>
       <c r="B75" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C75" s="27" t="inlineStr">
@@ -10431,7 +10670,7 @@
       </c>
       <c r="B76" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C76" s="27" t="inlineStr">
@@ -10473,7 +10712,7 @@
       </c>
       <c r="B77" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C77" s="27" t="inlineStr">
@@ -10515,7 +10754,7 @@
       </c>
       <c r="B78" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C78" s="27" t="inlineStr">
@@ -10557,7 +10796,7 @@
       </c>
       <c r="B79" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C79" s="27" t="inlineStr">
@@ -10599,7 +10838,7 @@
       </c>
       <c r="B80" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C80" s="27" t="inlineStr">
@@ -10641,7 +10880,7 @@
       </c>
       <c r="B81" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C81" s="27" t="inlineStr">
@@ -10683,7 +10922,7 @@
       </c>
       <c r="B82" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C82" s="27" t="inlineStr">
@@ -10725,7 +10964,7 @@
       </c>
       <c r="B83" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C83" s="27" t="inlineStr">
@@ -10767,7 +11006,7 @@
       </c>
       <c r="B84" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C84" s="27" t="inlineStr">
@@ -10809,7 +11048,7 @@
       </c>
       <c r="B85" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C85" s="27" t="inlineStr">
@@ -10851,7 +11090,7 @@
       </c>
       <c r="B86" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C86" s="27" t="inlineStr">
@@ -10893,7 +11132,7 @@
       </c>
       <c r="B87" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C87" s="27" t="inlineStr">
@@ -10935,7 +11174,7 @@
       </c>
       <c r="B88" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C88" s="27" t="inlineStr">
@@ -10977,7 +11216,7 @@
       </c>
       <c r="B89" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C89" s="27" t="inlineStr">
@@ -11019,7 +11258,7 @@
       </c>
       <c r="B90" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C90" s="27" t="inlineStr">
@@ -11061,7 +11300,7 @@
       </c>
       <c r="B91" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C91" s="27" t="inlineStr">
@@ -11103,7 +11342,7 @@
       </c>
       <c r="B92" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C92" s="27" t="inlineStr">
@@ -11145,7 +11384,7 @@
       </c>
       <c r="B93" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C93" s="27" t="inlineStr">
@@ -11187,7 +11426,7 @@
       </c>
       <c r="B94" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C94" s="27" t="inlineStr">
@@ -11229,7 +11468,7 @@
       </c>
       <c r="B95" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C95" s="27" t="inlineStr">
@@ -11271,7 +11510,7 @@
       </c>
       <c r="B96" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C96" s="27" t="inlineStr">
@@ -11313,7 +11552,7 @@
       </c>
       <c r="B97" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C97" s="27" t="inlineStr">
@@ -11355,7 +11594,7 @@
       </c>
       <c r="B98" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C98" s="27" t="inlineStr">
@@ -14211,7 +14450,7 @@
       </c>
       <c r="B166" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C166" s="27" t="inlineStr">
@@ -14253,7 +14492,7 @@
       </c>
       <c r="B167" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C167" s="27" t="inlineStr">
@@ -14295,7 +14534,7 @@
       </c>
       <c r="B168" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C168" s="27" t="inlineStr">
@@ -14337,7 +14576,7 @@
       </c>
       <c r="B169" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C169" s="27" t="inlineStr">
@@ -14379,7 +14618,7 @@
       </c>
       <c r="B170" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C170" s="27" t="inlineStr">
@@ -14421,7 +14660,7 @@
       </c>
       <c r="B171" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C171" s="27" t="inlineStr">
@@ -14463,7 +14702,7 @@
       </c>
       <c r="B172" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C172" s="27" t="inlineStr">
@@ -14505,7 +14744,7 @@
       </c>
       <c r="B173" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C173" s="27" t="inlineStr">
@@ -14547,7 +14786,7 @@
       </c>
       <c r="B174" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C174" s="27" t="inlineStr">
@@ -14589,7 +14828,7 @@
       </c>
       <c r="B175" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C175" s="27" t="inlineStr">
@@ -14631,7 +14870,7 @@
       </c>
       <c r="B176" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C176" s="27" t="inlineStr">
@@ -14673,7 +14912,7 @@
       </c>
       <c r="B177" s="27" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C177" s="27" t="inlineStr">
@@ -17277,7 +17516,7 @@
       </c>
       <c r="B239" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C239" s="27" t="inlineStr">
@@ -17319,7 +17558,7 @@
       </c>
       <c r="B240" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C240" s="27" t="inlineStr">
@@ -17361,7 +17600,7 @@
       </c>
       <c r="B241" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C241" s="27" t="inlineStr">
@@ -17403,7 +17642,7 @@
       </c>
       <c r="B242" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C242" s="27" t="inlineStr">
@@ -17445,7 +17684,7 @@
       </c>
       <c r="B243" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C243" s="27" t="inlineStr">
@@ -17487,7 +17726,7 @@
       </c>
       <c r="B244" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C244" s="27" t="inlineStr">
@@ -17529,7 +17768,7 @@
       </c>
       <c r="B245" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C245" s="27" t="inlineStr">
@@ -17571,7 +17810,7 @@
       </c>
       <c r="B246" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C246" s="27" t="inlineStr">
@@ -17613,7 +17852,7 @@
       </c>
       <c r="B247" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C247" s="27" t="inlineStr">
@@ -17655,7 +17894,7 @@
       </c>
       <c r="B248" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C248" s="27" t="inlineStr">
@@ -17697,7 +17936,7 @@
       </c>
       <c r="B249" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C249" s="27" t="inlineStr">
@@ -17739,7 +17978,7 @@
       </c>
       <c r="B250" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C250" s="27" t="inlineStr">
@@ -17781,7 +18020,7 @@
       </c>
       <c r="B251" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C251" s="27" t="inlineStr">
@@ -17823,7 +18062,7 @@
       </c>
       <c r="B252" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C252" s="27" t="inlineStr">
@@ -17865,7 +18104,7 @@
       </c>
       <c r="B253" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C253" s="27" t="inlineStr">
@@ -17907,7 +18146,7 @@
       </c>
       <c r="B254" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C254" s="27" t="inlineStr">
@@ -17949,7 +18188,7 @@
       </c>
       <c r="B255" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C255" s="27" t="inlineStr">
@@ -17991,7 +18230,7 @@
       </c>
       <c r="B256" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C256" s="27" t="inlineStr">
@@ -18033,7 +18272,7 @@
       </c>
       <c r="B257" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C257" s="27" t="inlineStr">
@@ -18075,7 +18314,7 @@
       </c>
       <c r="B258" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C258" s="27" t="inlineStr">
@@ -18117,7 +18356,7 @@
       </c>
       <c r="B259" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C259" s="27" t="inlineStr">
@@ -18159,7 +18398,7 @@
       </c>
       <c r="B260" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C260" s="27" t="inlineStr">
@@ -18201,7 +18440,7 @@
       </c>
       <c r="B261" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C261" s="27" t="inlineStr">
@@ -18243,7 +18482,7 @@
       </c>
       <c r="B262" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C262" s="27" t="inlineStr">
@@ -18285,7 +18524,7 @@
       </c>
       <c r="B263" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C263" s="27" t="inlineStr">
@@ -18327,7 +18566,7 @@
       </c>
       <c r="B264" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C264" s="27" t="inlineStr">
@@ -18369,7 +18608,7 @@
       </c>
       <c r="B265" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C265" s="27" t="inlineStr">
@@ -18411,7 +18650,7 @@
       </c>
       <c r="B266" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C266" s="27" t="inlineStr">
@@ -18453,7 +18692,7 @@
       </c>
       <c r="B267" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C267" s="27" t="inlineStr">
@@ -18495,7 +18734,7 @@
       </c>
       <c r="B268" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C268" s="27" t="inlineStr">
@@ -21225,7 +21464,7 @@
       </c>
       <c r="B333" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C333" s="27" t="inlineStr">
@@ -21267,7 +21506,7 @@
       </c>
       <c r="B334" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C334" s="27" t="inlineStr">
@@ -21309,7 +21548,7 @@
       </c>
       <c r="B335" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C335" s="27" t="inlineStr">
@@ -21351,7 +21590,7 @@
       </c>
       <c r="B336" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C336" s="27" t="inlineStr">
@@ -21393,7 +21632,7 @@
       </c>
       <c r="B337" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C337" s="27" t="inlineStr">
@@ -21435,7 +21674,7 @@
       </c>
       <c r="B338" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C338" s="27" t="inlineStr">
@@ -21477,7 +21716,7 @@
       </c>
       <c r="B339" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C339" s="27" t="inlineStr">
@@ -21519,7 +21758,7 @@
       </c>
       <c r="B340" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C340" s="27" t="inlineStr">
@@ -21561,7 +21800,7 @@
       </c>
       <c r="B341" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C341" s="27" t="inlineStr">
@@ -21603,7 +21842,7 @@
       </c>
       <c r="B342" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C342" s="27" t="inlineStr">
@@ -21645,7 +21884,7 @@
       </c>
       <c r="B343" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C343" s="27" t="inlineStr">
@@ -21687,7 +21926,7 @@
       </c>
       <c r="B344" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C344" s="27" t="inlineStr">
@@ -21729,7 +21968,7 @@
       </c>
       <c r="B345" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C345" s="27" t="inlineStr">
@@ -21771,7 +22010,7 @@
       </c>
       <c r="B346" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C346" s="27" t="inlineStr">
@@ -21813,7 +22052,7 @@
       </c>
       <c r="B347" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C347" s="27" t="inlineStr">
@@ -21855,7 +22094,7 @@
       </c>
       <c r="B348" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C348" s="27" t="inlineStr">
@@ -21897,7 +22136,7 @@
       </c>
       <c r="B349" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C349" s="27" t="inlineStr">
@@ -21939,7 +22178,7 @@
       </c>
       <c r="B350" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C350" s="27" t="inlineStr">
@@ -21981,7 +22220,7 @@
       </c>
       <c r="B351" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C351" s="27" t="inlineStr">
@@ -22023,7 +22262,7 @@
       </c>
       <c r="B352" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C352" s="27" t="inlineStr">
@@ -22065,7 +22304,7 @@
       </c>
       <c r="B353" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C353" s="27" t="inlineStr">
@@ -22107,7 +22346,7 @@
       </c>
       <c r="B354" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C354" s="27" t="inlineStr">
@@ -22149,7 +22388,7 @@
       </c>
       <c r="B355" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C355" s="27" t="inlineStr">
@@ -22191,7 +22430,7 @@
       </c>
       <c r="B356" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C356" s="27" t="inlineStr">
@@ -22233,7 +22472,7 @@
       </c>
       <c r="B357" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C357" s="27" t="inlineStr">
@@ -22275,7 +22514,7 @@
       </c>
       <c r="B358" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C358" s="27" t="inlineStr">
@@ -22317,7 +22556,7 @@
       </c>
       <c r="B359" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C359" s="27" t="inlineStr">
@@ -22359,7 +22598,7 @@
       </c>
       <c r="B360" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C360" s="27" t="inlineStr">
@@ -22401,7 +22640,7 @@
       </c>
       <c r="B361" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C361" s="27" t="inlineStr">
@@ -22443,7 +22682,7 @@
       </c>
       <c r="B362" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C362" s="27" t="inlineStr">
@@ -22485,7 +22724,7 @@
       </c>
       <c r="B363" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C363" s="27" t="inlineStr">
@@ -22527,7 +22766,7 @@
       </c>
       <c r="B364" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C364" s="27" t="inlineStr">
@@ -25635,7 +25874,7 @@
       </c>
       <c r="B438" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C438" s="27" t="inlineStr">
@@ -25677,7 +25916,7 @@
       </c>
       <c r="B439" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C439" s="27" t="inlineStr">
@@ -25719,7 +25958,7 @@
       </c>
       <c r="B440" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C440" s="27" t="inlineStr">
@@ -25761,7 +26000,7 @@
       </c>
       <c r="B441" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C441" s="27" t="inlineStr">
@@ -25803,7 +26042,7 @@
       </c>
       <c r="B442" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C442" s="27" t="inlineStr">
@@ -25845,7 +26084,7 @@
       </c>
       <c r="B443" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C443" s="27" t="inlineStr">
@@ -25887,7 +26126,7 @@
       </c>
       <c r="B444" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C444" s="27" t="inlineStr">
@@ -25929,7 +26168,7 @@
       </c>
       <c r="B445" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C445" s="27" t="inlineStr">
@@ -25971,7 +26210,7 @@
       </c>
       <c r="B446" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C446" s="27" t="inlineStr">
@@ -26013,7 +26252,7 @@
       </c>
       <c r="B447" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C447" s="27" t="inlineStr">
@@ -26055,7 +26294,7 @@
       </c>
       <c r="B448" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C448" s="27" t="inlineStr">
@@ -26097,7 +26336,7 @@
       </c>
       <c r="B449" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C449" s="27" t="inlineStr">
@@ -26139,7 +26378,7 @@
       </c>
       <c r="B450" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C450" s="27" t="inlineStr">
@@ -26181,7 +26420,7 @@
       </c>
       <c r="B451" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C451" s="27" t="inlineStr">
@@ -26223,7 +26462,7 @@
       </c>
       <c r="B452" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C452" s="27" t="inlineStr">
@@ -26265,7 +26504,7 @@
       </c>
       <c r="B453" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C453" s="27" t="inlineStr">
@@ -26307,7 +26546,7 @@
       </c>
       <c r="B454" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C454" s="27" t="inlineStr">
@@ -26349,7 +26588,7 @@
       </c>
       <c r="B455" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C455" s="27" t="inlineStr">
@@ -26391,7 +26630,7 @@
       </c>
       <c r="B456" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C456" s="27" t="inlineStr">
@@ -26433,7 +26672,7 @@
       </c>
       <c r="B457" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C457" s="27" t="inlineStr">
@@ -26475,7 +26714,7 @@
       </c>
       <c r="B458" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C458" s="27" t="inlineStr">
@@ -26517,7 +26756,7 @@
       </c>
       <c r="B459" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C459" s="27" t="inlineStr">
@@ -26559,7 +26798,7 @@
       </c>
       <c r="B460" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C460" s="27" t="inlineStr">
@@ -26601,7 +26840,7 @@
       </c>
       <c r="B461" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C461" s="27" t="inlineStr">
@@ -26643,7 +26882,7 @@
       </c>
       <c r="B462" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C462" s="27" t="inlineStr">
@@ -26685,7 +26924,7 @@
       </c>
       <c r="B463" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C463" s="27" t="inlineStr">
@@ -26727,7 +26966,7 @@
       </c>
       <c r="B464" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C464" s="27" t="inlineStr">
@@ -26769,7 +27008,7 @@
       </c>
       <c r="B465" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C465" s="27" t="inlineStr">
@@ -27021,7 +27260,7 @@
       </c>
       <c r="B471" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C471" s="27" t="inlineStr">
@@ -27063,7 +27302,7 @@
       </c>
       <c r="B472" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C472" s="27" t="inlineStr">
@@ -27105,7 +27344,7 @@
       </c>
       <c r="B473" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C473" s="27" t="inlineStr">
@@ -27147,7 +27386,7 @@
       </c>
       <c r="B474" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C474" s="27" t="inlineStr">
@@ -27189,7 +27428,7 @@
       </c>
       <c r="B475" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C475" s="27" t="inlineStr">
@@ -27231,7 +27470,7 @@
       </c>
       <c r="B476" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C476" s="27" t="inlineStr">
@@ -27273,7 +27512,7 @@
       </c>
       <c r="B477" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C477" s="27" t="inlineStr">
@@ -27315,7 +27554,7 @@
       </c>
       <c r="B478" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C478" s="27" t="inlineStr">
@@ -27357,7 +27596,7 @@
       </c>
       <c r="B479" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C479" s="27" t="inlineStr">
@@ -27399,7 +27638,7 @@
       </c>
       <c r="B480" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C480" s="27" t="inlineStr">
@@ -27441,7 +27680,7 @@
       </c>
       <c r="B481" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C481" s="27" t="inlineStr">
@@ -27483,7 +27722,7 @@
       </c>
       <c r="B482" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C482" s="27" t="inlineStr">
@@ -27525,7 +27764,7 @@
       </c>
       <c r="B483" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C483" s="27" t="inlineStr">
@@ -27567,7 +27806,7 @@
       </c>
       <c r="B484" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C484" s="27" t="inlineStr">
@@ -27609,7 +27848,7 @@
       </c>
       <c r="B485" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C485" s="27" t="inlineStr">
@@ -27651,7 +27890,7 @@
       </c>
       <c r="B486" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C486" s="27" t="inlineStr">
@@ -27693,7 +27932,7 @@
       </c>
       <c r="B487" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C487" s="27" t="inlineStr">
@@ -27735,7 +27974,7 @@
       </c>
       <c r="B488" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C488" s="27" t="inlineStr">
@@ -27777,7 +28016,7 @@
       </c>
       <c r="B489" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C489" s="27" t="inlineStr">
@@ -27819,7 +28058,7 @@
       </c>
       <c r="B490" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C490" s="27" t="inlineStr">
@@ -27861,7 +28100,7 @@
       </c>
       <c r="B491" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C491" s="27" t="inlineStr">
@@ -27903,7 +28142,7 @@
       </c>
       <c r="B492" s="27" t="inlineStr">
         <is>
-          <t>FENNEL-CONDITIONAL</t>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C492" s="27" t="inlineStr">
@@ -31297,9 +31536,9 @@
           <t>Boost in a Bottle</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-COND.</t>
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -31320,7 +31559,7 @@
       </c>
       <c r="G19" s="17" t="inlineStr">
         <is>
-          <t>Use with awareness — Tisserand+Shelton say fennel is not directly convulsant. On storm days (Kp≥4), be aware that fennel inhibits CYP3A4, the enzyme that metabolizes Theo's clorazepate and midazolam rescue meds. If rescue is needed, allow extra time after topical fennel application.</t>
+          <t>FENNEL+OREGANO-CONDITIONAL — case-by-case use. Two flags stacking: (1) Fennel CYP3A4 inhibition (Subehan 2007) — relevant to Theo because clorazepate/midazolam (rescue meds) are CYP3A4 substrates; storm-day timing matters. Levetiracetam unaffected. (2) Oregano canine evidence uncertainty — per Merck Vet Manual, dogs glucuronidate phenols efficiently. Hot-oil phenol character real, but documented harm at dilute multi-oil concentrations absent in peer-reviewed canine literature. Neither flag rises to hard avoid.</t>
         </is>
       </c>
     </row>
@@ -31363,9 +31602,9 @@
           <t>KittyBoost</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-COND.</t>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr">
@@ -31386,7 +31625,7 @@
       </c>
       <c r="G21" s="17" t="inlineStr">
         <is>
-          <t>Use with awareness — Tisserand+Shelton say fennel is not directly convulsant. On storm days (Kp≥4), be aware that fennel inhibits CYP3A4, the enzyme that metabolizes Theo's clorazepate and midazolam rescue meds. If rescue is needed, allow extra time after topical fennel application.</t>
+          <t>FENNEL+OREGANO-CONDITIONAL — case-by-case use. Two flags stacking: (1) Fennel CYP3A4 inhibition (Subehan 2007) — relevant to Theo because clorazepate/midazolam (rescue meds) are CYP3A4 substrates; storm-day timing matters. Levetiracetam unaffected. (2) Oregano canine evidence uncertainty — per Merck Vet Manual, dogs glucuronidate phenols efficiently. Hot-oil phenol character real, but documented harm at dilute multi-oil concentrations absent in peer-reviewed canine literature. Neither flag rises to hard avoid.</t>
         </is>
       </c>
     </row>
@@ -31396,9 +31635,9 @@
           <t>KittyBoost LITE</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-COND.</t>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -31419,7 +31658,7 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>Use with awareness — Tisserand+Shelton say fennel is not directly convulsant. On storm days (Kp≥4), be aware that fennel inhibits CYP3A4, the enzyme that metabolizes Theo's clorazepate and midazolam rescue meds. If rescue is needed, allow extra time after topical fennel application.</t>
+          <t>FENNEL+OREGANO-CONDITIONAL — case-by-case use. Two flags stacking: (1) Fennel CYP3A4 inhibition (Subehan 2007) — relevant to Theo because clorazepate/midazolam (rescue meds) are CYP3A4 substrates; storm-day timing matters. Levetiracetam unaffected. (2) Oregano canine evidence uncertainty — per Merck Vet Manual, dogs glucuronidate phenols efficiently. Hot-oil phenol character real, but documented harm at dilute multi-oil concentrations absent in peer-reviewed canine literature. Neither flag rises to hard avoid.</t>
         </is>
       </c>
     </row>
@@ -31429,9 +31668,9 @@
           <t>NeuroBoost RTU</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-COND.</t>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
@@ -31452,7 +31691,7 @@
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
-          <t>Use with awareness — Tisserand+Shelton say fennel is not directly convulsant. On storm days (Kp≥4), be aware that fennel inhibits CYP3A4, the enzyme that metabolizes Theo's clorazepate and midazolam rescue meds. If rescue is needed, allow extra time after topical fennel application.</t>
+          <t>THEO'S ACTIVE ROTATION — CONTINUED USE CONFIRMED. NeuroBoost RTU is the AnimalEO-recommended seizure protocol blend. Both fennel and oregano flags acknowledged; neither rises to hard avoid. FENNEL: CYP3A4 inhibition relevant on storm days when rescue dosing of clorazepate/midazolam is more likely — allow extra time after topical application. Levetiracetam metabolism unaffected. OREGANO: per Merck Vet Manual + Savides 1980, dogs glucuronidate phenols efficiently (the SEO 'deadly in oil' narrative is cat physiology, not dog). Hot-oil character is a real consideration but documented harm at dilute multi-oil concentrations is absent in peer-reviewed canine literature.</t>
         </is>
       </c>
     </row>
@@ -31462,9 +31701,9 @@
           <t>SugarBalance</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-COND.</t>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
@@ -31485,7 +31724,7 @@
       </c>
       <c r="G24" s="17" t="inlineStr">
         <is>
-          <t>Use with awareness — Tisserand+Shelton say fennel is not directly convulsant. On storm days (Kp≥4), be aware that fennel inhibits CYP3A4, the enzyme that metabolizes Theo's clorazepate and midazolam rescue meds. If rescue is needed, allow extra time after topical fennel application.</t>
+          <t>FENNEL+OREGANO-CONDITIONAL — case-by-case use. Two flags stacking: (1) Fennel CYP3A4 inhibition (Subehan 2007) — relevant to Theo because clorazepate/midazolam (rescue meds) are CYP3A4 substrates; storm-day timing matters. Levetiracetam unaffected. (2) Oregano canine evidence uncertainty — per Merck Vet Manual, dogs glucuronidate phenols efficiently. Hot-oil phenol character real, but documented harm at dilute multi-oil concentrations absent in peer-reviewed canine literature. Neither flag rises to hard avoid.</t>
         </is>
       </c>
     </row>
@@ -31495,9 +31734,9 @@
           <t>ThyroBalance</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>FENNEL-COND.</t>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>FENNEL+OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -31518,7 +31757,7 @@
       </c>
       <c r="G25" s="17" t="inlineStr">
         <is>
-          <t>Use with awareness — Tisserand+Shelton say fennel is not directly convulsant. On storm days (Kp≥4), be aware that fennel inhibits CYP3A4, the enzyme that metabolizes Theo's clorazepate and midazolam rescue meds. If rescue is needed, allow extra time after topical fennel application.</t>
+          <t>FENNEL+OREGANO-CONDITIONAL — case-by-case use. Two flags stacking: (1) Fennel CYP3A4 inhibition (Subehan 2007) — relevant to Theo because clorazepate/midazolam (rescue meds) are CYP3A4 substrates; storm-day timing matters. Levetiracetam unaffected. (2) Oregano canine evidence uncertainty — per Merck Vet Manual, dogs glucuronidate phenols efficiently. Hot-oil phenol character real, but documented harm at dilute multi-oil concentrations absent in peer-reviewed canine literature. Neither flag rises to hard avoid.</t>
         </is>
       </c>
     </row>
@@ -31627,9 +31866,9 @@
           <t>AromaBoost #1 (RTU)</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>CLEAN</t>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
@@ -31650,7 +31889,7 @@
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Safe by ingredient profile. Use per AnimalEO guidance.</t>
+          <t>OREGANO-CONDITIONAL — case-by-case use, not routine rotation. Oregano contributes a hot-oil phenol component. Canine evidence is thin in both directions: no published case series of harm from dilute oregano in multi-oil blends, no safety trial establishing a therapeutic window. Per Merck Vet Manual + Court 2013 + Savides 1980, dogs glucuronidate phenols efficiently (the "dogs lack glucuronidation" SEO claim is cat physiology). Skin irritation from concentrate is the concrete concern. Single oregano EO = AVOID; this dilute blend = acceptable for occasional use.</t>
         </is>
       </c>
     </row>
@@ -31761,7 +32000,7 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -31782,7 +32021,7 @@
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>Safe by ingredient profile. Use per AnimalEO guidance.</t>
+          <t>CONDITIONAL — reclassified from CLEAN due to Citronella content. ASPCA / Pet Poison Helpline / VCA document canine-specific neurological caution for citronella regardless of favorable rodent anticonvulsant data. Avoid for Theo unless TCVM vet specifically approves.</t>
         </is>
       </c>
     </row>
@@ -31794,7 +32033,7 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>CONDITIONAL</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
@@ -31815,7 +32054,7 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>Safe by ingredient profile. Use per AnimalEO guidance.</t>
+          <t>CONDITIONAL — reclassified from CLEAN for framework consistency. Cleaning blend (residual surface contact + inhalation exposure for Theo). Citronella canine-caution applies regardless of labeled use. Use with normal household cleaning precautions; minimize Theo's contact during application.</t>
         </is>
       </c>
     </row>
@@ -32056,9 +32295,9 @@
           <t>Dump-a-Lump</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>CLEAN</t>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>OREGANO-CONDITIONAL</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
@@ -32079,7 +32318,7 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Safe by ingredient profile. Use per AnimalEO guidance.</t>
+          <t>OREGANO-CONDITIONAL — case-by-case use, not routine rotation. Oregano contributes a hot-oil phenol component. Canine evidence is thin in both directions: no published case series of harm from dilute oregano in multi-oil blends, no safety trial establishing a therapeutic window. Per Merck Vet Manual + Court 2013 + Savides 1980, dogs glucuronidate phenols efficiently (the "dogs lack glucuronidation" SEO claim is cat physiology). Skin irritation from concentrate is the concrete concern. Single oregano EO = AVOID; this dilute blend = acceptable for occasional use.</t>
         </is>
       </c>
     </row>
@@ -34631,17 +34870,17 @@
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>Carvacrol/thymol — hot oil, dermal irritant. Some carvacrol anticonvulsant data but not used in seizure protocols.</t>
+          <t>Carvacrol (60-80%) + thymol — high-phenol 'hot oil' class. Mechanism evidence FAVORS oregano: Manville 2014 (6Hz seizure ED50 = 35.8 mg/kg, PI = 5.3), Hosseini 2018 (LPS-induced proconvulsant mitigation via COX-2). NOT on Tisserand convulsant list. BUT: no peer-reviewed canine case series of harm OR safety; no established canine therapeutic window; Tisserand 2014 LD50 = 480 mg/kg (narrow margin vs typical kitchen herbs); Fereydooni 2023 Open Vet J uses 5% topical carvacrol as demodicosis treatment. Pet-blog 'dogs lack glucuronidation' claim is factually wrong — that's cat physiology (Merck Vet Manual; Savides 1980 shows dogs glucuronidate phenols MORE efficiently than cats).</t>
         </is>
       </c>
       <c r="E71" s="21" t="inlineStr">
         <is>
-          <t>Avoid during active-seizure window.</t>
+          <t>AVOID single use (strengthened from 'avoid during active-seizure window'). Use as one of many ingredients in properly diluted AnimalEO multi-oil blends is acceptable (see OREGANO-CONDITIONAL and FENNEL+OREGANO-CONDITIONAL tiers in Blends tab). Direct single application to Theo's skin or via diffuser is not warranted given thin canine safety evidence and hot-oil dermal irritation potential. Single carvacrol oil products marketed as 'natural antibiotic' for dogs lack peer-reviewed safety basis.</t>
         </is>
       </c>
       <c r="F71" s="21" t="inlineStr">
         <is>
-          <t>Hot oil class</t>
+          <t>Hot oil class · canine evidence thin both directions</t>
         </is>
       </c>
     </row>
